--- a/E/RCIX4N.xlsx
+++ b/E/RCIX4N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="86">
   <si>
     <t/>
   </si>
@@ -127,30 +127,54 @@
     <t>CMPN TROPICANA.CHO65</t>
   </si>
   <si>
+    <t>11</t>
+  </si>
+  <si>
     <t>20016706</t>
   </si>
   <si>
     <t>CAMPN SPNGBOB PCK 70</t>
   </si>
   <si>
+    <t>12</t>
+  </si>
+  <si>
     <t>20078821</t>
   </si>
   <si>
     <t>CMPNA SPDRMAN STR 55</t>
   </si>
   <si>
+    <t>13</t>
+  </si>
+  <si>
     <t>20134924</t>
   </si>
   <si>
     <t>CMPNA ICE RNBW POP60</t>
   </si>
   <si>
+    <t>14</t>
+  </si>
+  <si>
     <t>20135663</t>
   </si>
   <si>
     <t>CMPN CNCRTO ICOWNC80</t>
   </si>
   <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>20142762</t>
+  </si>
+  <si>
+    <t>CMPN OLYMP CHOVAN 80</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
     <t>20140182</t>
   </si>
   <si>
@@ -229,25 +253,16 @@
     <t>CMPNA HULA DURIAN 90</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
     <t>20141543</t>
   </si>
   <si>
     <t>CMPN NEAPOLITAN 160</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
     <t>20134922</t>
   </si>
   <si>
     <t>CMPN ICE STRW LIME70</t>
-  </si>
-  <si>
-    <t>999</t>
   </si>
   <si>
     <t>20134455</t>
@@ -646,13 +661,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="5" customWidth="1"/>
+    <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="4" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
@@ -888,10 +903,10 @@
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>5</v>
@@ -899,19 +914,19 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>9</v>
@@ -919,19 +934,19 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>5</v>
@@ -939,19 +954,19 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>26</v>
@@ -959,19 +974,19 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>26</v>
@@ -979,19 +994,19 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>26</v>
@@ -999,10 +1014,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -1011,7 +1026,7 @@
         <v>8</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>26</v>
@@ -1019,10 +1034,10 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -1031,7 +1046,7 @@
         <v>8</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>26</v>
@@ -1039,39 +1054,39 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F20" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>5</v>
@@ -1079,19 +1094,19 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>5</v>
@@ -1099,19 +1114,19 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>5</v>
@@ -1119,59 +1134,59 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>26</v>
@@ -1179,19 +1194,19 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>26</v>
@@ -1199,19 +1214,19 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>26</v>
@@ -1219,59 +1234,59 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>78</v>
+        <v>8</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>26</v>
@@ -1279,21 +1294,41 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>78</v>
+        <v>8</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="F32" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F33" s="1" t="s">
         <v>26</v>
       </c>
     </row>

--- a/E/RCIX4N.xlsx
+++ b/E/RCIX4N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="84">
   <si>
     <t/>
   </si>
@@ -209,12 +209,6 @@
   </si>
   <si>
     <t>CAMPINA HAPPY COW 85</t>
-  </si>
-  <si>
-    <t>20114107</t>
-  </si>
-  <si>
-    <t>CNCERTO SNDAE CHO110</t>
   </si>
   <si>
     <t>20121363</t>
@@ -661,7 +655,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1146,10 +1140,10 @@
         <v>8</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1166,10 +1160,10 @@
         <v>8</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1186,7 +1180,7 @@
         <v>8</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>26</v>
@@ -1206,7 +1200,7 @@
         <v>8</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>26</v>
@@ -1226,7 +1220,7 @@
         <v>8</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>26</v>
@@ -1246,10 +1240,10 @@
         <v>8</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1266,10 +1260,10 @@
         <v>8</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1286,7 +1280,7 @@
         <v>8</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>26</v>
@@ -1306,29 +1300,9 @@
         <v>8</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F33" s="1" t="s">
         <v>26</v>
       </c>
     </row>
